--- a/daily_matches/job_matches_2026-05-15.xlsx
+++ b/daily_matches/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Engineer - Test Automation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ryan, LLC</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,147 +486,147 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, XGBoost, Keras</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, BigQuery, Kubernetes, Jenkins, Git, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706efe02ae79f4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb42007cbd45836e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RH Digital Strategy and Merchandising</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>JustPaid</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Corte Madera, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, S3, Glue, Athena, BigQuery, Docker, Apache Airflow</t>
+          <t>TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ff12aace30b55c</t>
+          <t>https://www.indeed.com/viewjob?jk=27aacac9d59c4cf3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RepliGen Corporation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, CI/CD</t>
+          <t>Generative AI, RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604e545272709db4</t>
+          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, CI/CD, Jenkins, GitHub Actions, Git, Snowflake</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Terraform, Hadoop, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Scientist - Remote</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tower Hill Insurance Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gainesville, FL, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, PyTorch, S3, Glue, FastAPI, Snowflake, PySpark, PostgreSQL, Power BI</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Terraform, Hadoop, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3701a8f48a54cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,116 +657,116 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, Azure ML, FastAPI, Docker, Kubernetes, Git</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Terraform, Hadoop, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c5d8670422df37</t>
+          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Git, Snowflake, Redshift, Kafka, Hadoop, MySQL, Cassandra, NoSQL</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Terraform, Hadoop, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
+          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402d9ccd9278b80f</t>
+          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Solution Architect - Agentic AI &amp; Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, Redshift, Kubernetes, AKS, Terraform, Redshift, Kafka</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae7bf11c539daa6</t>
+          <t>https://www.indeed.com/viewjob?jk=b507c7b6e9aa4f16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, Redshift, Kubernetes, AKS, Terraform, Redshift, Kafka</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619f0f0e3a4ac4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, Redshift, Kubernetes, AKS, Terraform, Redshift, Kafka</t>
+          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d0de22265232e</t>
+          <t>https://www.indeed.com/viewjob?jk=b89b51e1e35eb367</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, Redshift, Kubernetes, AKS, Terraform, Redshift, Kafka</t>
+          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,207 +881,207 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71cabdc237f48ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=9c3c3dd72993d47a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a11e9d2a751b0a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Technical Consultant/Engineer</t>
+          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Convr</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Cumberland, RI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, Snowflake, MySQL, Cassandra, NoSQL, Python</t>
+          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df8deed0f9f014f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2de39849baa5ce9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL</t>
+          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebf5891f08bccba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, BigQuery, Redshift, Python</t>
+          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb81d75d1bd7d57c</t>
+          <t>https://www.indeed.com/viewjob?jk=a01ff8892b52306b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineering Associate - Applications, Data &amp; AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, BigQuery, Redshift, Python</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1731beb41cb17a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7b495a739932fb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, BigQuery, Redshift, Python</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0cc97d0b234ff83</t>
+          <t>https://www.indeed.com/viewjob?jk=f3066fd53108cbf4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>RAG, LLaMA, Copilot, TensorFlow, PyTorch, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,137 +1126,137 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c0c4067f6a1bf1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - MarTech(Remote)</t>
+          <t>AI Engineer | Onsite San Diego HQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rula</t>
+          <t>Neurocrine Biosciences</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670b706cdb1ca17b</t>
+          <t>https://www.indeed.com/viewjob?jk=be9d2763756403bc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist - AI Agents</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>2U</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, R</t>
+          <t>Data Scientist, RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=920e0c394bfc8cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=e072650f295cc478</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>AO REED</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, TensorFlow, PyTorch, CI/CD, Git, Power BI, Python, SQL</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e4a7d51746f638</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c7d870bea56ec6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Head Computer Vision &amp; AI Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>PyTorch, OpenCV, S3, EC2, MLflow, Databricks, PySpark, Python, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f37911d921315d84</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure App Modernization &amp; DevOps Customer Engineer</t>
+          <t>Data Scientist Associate - Payments</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JDA TSG</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee79fad727fa6632</t>
+          <t>https://www.indeed.com/viewjob?jk=987f69ca4dc870a7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Potawatomi Federal Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4068381ee6ee32a7</t>
+          <t>https://www.indeed.com/viewjob?jk=679d1d3b3b6b7f3a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Scientist - Specialty Operations</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TP ICAP</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Kafka, MongoDB, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2d120f52ff192b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e38c6695f1d823e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AdvancedMD</t>
+          <t>Ormat Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Copilot, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bf944d44d155a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7a0840298bd497</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer</t>
+          <t>Data Scientist - Specialty Operations</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AdvancedMD</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6437044812b337e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb9b702c088dac6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>AI Web Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Command Cyber Solutions</t>
+          <t>Pebble Mobility</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Docker, CI/CD, Git, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,812 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6829c961c144999</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PragerU</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, S3, Git, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80ebe249e47759f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Computer Scientist / Software Developer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Integrated Solutions for Systems</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Auburn, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a50d0d722ad774</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Computer Scientist / Software Developer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Integrated Solutions for Systems</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Aberdeen, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00c0dbd2c9240e41</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AI Engineer - Agent Automation</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Zoom Communications</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, PyTorch, Docker, Kubernetes, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae641e3014fcf681</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer - Generative AI</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac293e9df2b8a0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Copilot &amp; Azure AI Foundry Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>The Hearst Corporation</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=094a2e3e371412d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Copilot &amp; Azure AI Foundry Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>The Hearst Corporation</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=024172d120541b69</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Cadent</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, AKS, PySpark, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa812b7342e02361</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AI Development Architect</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Post University</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Waterbury, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Data Lake, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c2a45d0a15b35bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Software Development Engineer 5, Enterprise GenAI</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=517d91e3ee081632</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Test Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Autodesk</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, MLflow, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3a1279fc588cf8</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full Stack</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Information Technology Senior Management Forum</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6577d30405ec6adf</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Co-Op: Financial Data Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>The Clorox Company</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72d4d971d03244d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer in Quality Engineering</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dde379f9b2b5543d</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>The Cigna Group</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Data Lake, Kubernetes, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AI Engineering Intern (LLM Applications)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Frontline Education</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Wayne, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, PyTorch, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35493778bd73b50b</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Research Scientist, Operations Research (Infrastructure Lab)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>ByteDance</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4bc4af5f4a297b</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Research Scientist, Operations Research (Infrastructure Lab)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>ByteDance</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cab6b666dae2e1f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Research Scientist, Operations Research (Infrastructure Lab)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>ByteDance</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=313674f13dc8476a</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Research Scientist, Operations Research (Infrastructure Lab)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>ByteDance</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23abe40d959f0121</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Labcorp</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56991e56f5dc24c4</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8a62a3da405960</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-15.xlsx
+++ b/daily_matches/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer - Test Automation</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, BigQuery, Kubernetes, Jenkins, Git, BigQuery</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, FAISS, Pinecone, S3, Glue, Kinesis, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb42007cbd45836e</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JustPaid</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, BigQuery, Redshift, PySpark, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27aacac9d59c4cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Databricks, Redshift</t>
+          <t>Copilot, BigQuery, Kinesis, Git, Snowflake, Databricks, BigQuery, Kafka, MySQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+          <t>https://www.indeed.com/viewjob?jk=f778e82eb9d3a8f1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Terraform, Hadoop, Python</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Applications Architect (Global Security Class Actions)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Terraform, Hadoop, Python</t>
+          <t>RAG, CI/CD, Jenkins, Terraform, Git, Kafka, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2b2937ebe949351</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Terraform, Hadoop, Python</t>
+          <t>Data Scientist, Kinesis, Kubernetes, CI/CD, Terraform, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a6a4f3024f55a5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Stretto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Terraform, Hadoop, Python</t>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
+          <t>https://www.indeed.com/viewjob?jk=caa555968d963b23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Stretto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=c5d858080e7b74aa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solution Architect - Agentic AI &amp; Data</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Stretto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b507c7b6e9aa4f16</t>
+          <t>https://www.indeed.com/viewjob?jk=2075b9bdba4a5cf1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Threat Detection Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=363319a5fec305ca</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b89b51e1e35eb367</t>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
+          <t>Senior Data Engineer - People Technology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SolarWinds</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
+          <t>BigQuery, CI/CD, Terraform, Git, BigQuery, Tableau, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c3c3dd72993d47a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ba506b254d536</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
+          <t>RAG, Dataflow, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a11e9d2a751b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cumberland, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,532 +951,112 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2de39849baa5ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=95c775efb7940ca6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebf5891f08bccba</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d7c30aff2299ca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Agentic AI &amp; Messaging Platforms</t>
+          <t>Senior Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, Dataflow, BigQuery, Kafka, Python, R</t>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01ff8892b52306b</t>
+          <t>https://www.indeed.com/viewjob?jk=6640c9d970e690ed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineering Associate - Applications, Data &amp; AI</t>
+          <t>Cloud Security Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7b495a739932fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AI Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TDIndustries</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3066fd53108cbf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior AI DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, Copilot, TensorFlow, PyTorch, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c0c4067f6a1bf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AI Engineer | Onsite San Diego HQ</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Neurocrine Biosciences</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be9d2763756403bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2U</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e072650f295cc478</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>AO REED</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Beltsville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c7d870bea56ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Head Computer Vision &amp; AI Scientist</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SportsBiz Group Inc</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>PyTorch, OpenCV, S3, EC2, MLflow, Databricks, PySpark, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f37911d921315d84</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Scientist Associate - Payments</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=987f69ca4dc870a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=679d1d3b3b6b7f3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Scientist - Specialty Operations</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Python, SQL, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e38c6695f1d823e</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Ormat Technologies</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7a0840298bd497</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Data Scientist - Specialty Operations</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Python, SQL, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb9b702c088dac6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AI Web Developer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Pebble Mobility</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, CI/CD, Git, R, Java</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8a62a3da405960</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7e882b5322bf28</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-15.xlsx
+++ b/daily_matches/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Database Engineer - Platform Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>IntegriChain</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, FAISS, Pinecone, S3, Glue, Kinesis, Databricks</t>
+          <t>RAG, AWS SageMaker, S3, Glue, Redshift, Synapse, Data Lake, Kinesis, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2a75955286c43d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>PGW Auto Glass</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, BigQuery, Redshift, PySpark, Kafka, PostgreSQL, MySQL</t>
+          <t>RAG, Copilot, Synapse, Data Lake, Docker, Apache Airflow, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3d77615dc2cb49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AI Engineer-Remote Opportunity</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Answer Financial Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, BigQuery, Kinesis, Git, Snowflake, Databricks, BigQuery, Kafka, MySQL, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f778e82eb9d3a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=cde2c2e9e32124c1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>IT Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Keras, BigQuery, MLflow, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4da1ec7809293f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Applications Architect (Global Security Class Actions)</t>
+          <t>JD - Senior Software Engineer 1, ML</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Git, Kafka, NoSQL, SQL, R, Java</t>
+          <t>RAG, Pinecone, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, FastAPI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b2937ebe949351</t>
+          <t>https://www.indeed.com/viewjob?jk=d672ede61ebda4d7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Kinesis, Kubernetes, CI/CD, Terraform, Kafka, Python, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Copilot, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a6a4f3024f55a5</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stretto</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa555968d963b23</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stretto</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5d858080e7b74aa</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stretto</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2075b9bdba4a5cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363319a5fec305ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - People Technology</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BigQuery, CI/CD, Terraform, Git, BigQuery, Tableau, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ba506b254d536</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Product Engineer, Alternatives</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>PIMCO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Data Lake, MLflow, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,112 +951,602 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c775efb7940ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=85493af98c332665</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Databricks Architect | US</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
+          <t>LangChain, Data Lake, MLflow, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d7c30aff2299ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack</t>
+          <t>Data Scientist - Pricing and Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PGW Auto Glass</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Copilot, Synapse, Dataflow, PySpark, Kafka, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6640c9d970e690ed</t>
+          <t>https://www.indeed.com/viewjob?jk=884dcd1e8f112af1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Security Architect</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, Data Lake, Git, PostgreSQL, MongoDB, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Apptronik</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=357fe3501b7836a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Thia</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, PyTorch, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bb23d18bfacac08</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Thia</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c260c02f5a9d573</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer: $150-170,000, 5+ Years Required, MN Based, Hybrid - 2 Days in Office</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GovDocs</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7e882b5322bf28</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, MongoDB, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92c0b8b83d100d40</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Consultant, Cloud Solutions</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Burwood Group</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Camping World</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lincolnshire, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, AKS, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea3d25d3552f3f14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Backend Engineer, ML Systems</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Thia</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2bbddda0640b383</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Snap Finance</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05422269350bcaa3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Solutions Specialist-Remote Opportunity</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Answer Financial Inc.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, LLaMA, Gemini, Copilot, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08437d2060737567</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer IV $80,000- $130,000 DOE- Remote</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ELM Utility Services</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acfcda59315648d1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-15.xlsx
+++ b/daily_matches/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Platform Engineering</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IntegriChain</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, Glue, Redshift, Synapse, Data Lake, Kinesis, MLflow, CI/CD</t>
+          <t>Data Scientist, RAG, S3, Data Lake, Kinesis, MLflow, Apache Airflow, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2a75955286c43d</t>
+          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure &amp; Microsoft Fabric Platform</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PGW Auto Glass</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Data Lake, Docker, Apache Airflow, CI/CD, Terraform, Git, Snowflake</t>
+          <t>Data Scientist, RAG, S3, Data Lake, Kinesis, MLflow, Apache Airflow, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3d77615dc2cb49</t>
+          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer-Remote Opportunity</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Answer Financial Inc.</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>Data Scientist, RAG, S3, Data Lake, Kinesis, MLflow, Apache Airflow, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde2c2e9e32124c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IT Data Scientist</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Keras, BigQuery, MLflow, CI/CD, Databricks</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, MySQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4da1ec7809293f</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JD - Senior Software Engineer 1, ML</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Ocrolus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, FastAPI, Docker, Kubernetes, Git</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d672ede61ebda4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6ab699a2979fd4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Machine Learning Engineer, Zeitgeist, Personalization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Dataflow, BigQuery, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=f665777ed787bc0c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=f03269999a92f7e0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Salesforce Platform Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+          <t>RAG, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=83b4c7d66e6190b4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior DevOps Engineer- Arlington, VA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=896ef6d5605394c3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=46ef10fbacb00408</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>BioPharma Consulting JAD Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Juncos, PR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Keras, OpenCV, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b2154184df56d96</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Product Engineer, Alternatives</t>
+          <t>Data Scientist - Production Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PIMCO</t>
+          <t>Cordial Experience</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Data Lake, MLflow, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>Data Scientist, S3, Glue, Athena, BigQuery, Snowflake, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85493af98c332665</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5485c21d8416d6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Architect | US</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, Data Lake, MLflow, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Python</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
+          <t>https://www.indeed.com/viewjob?jk=c6277a4a2f289d56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist - Pricing and Analytics</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PGW Auto Glass</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Synapse, Dataflow, PySpark, Kafka, Power BI, Python, SQL</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=884dcd1e8f112af1</t>
+          <t>https://www.indeed.com/viewjob?jk=02ccbdb3f245768d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Sr. Software Quality Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Data Lake, Git, PostgreSQL, MongoDB, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a013f13e8069e9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357fe3501b7836a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Software Engineer, AI Agents &amp; Generative AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=305217c9c3762b47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Software Engineer, AI Agents &amp; Generative AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b85021dc7273ef59</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, Kubernetes, Git, BigQuery, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=29456fe99404592c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=b3677f7a6bce9ab7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer - 1010</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Thia</t>
+          <t>Lightcast</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Terraform, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bb23d18bfacac08</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc8d849e742b5b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Data Engineer - 1010</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Thia</t>
+          <t>Lightcast</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Moscow, ID, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Terraform, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c260c02f5a9d573</t>
+          <t>https://www.indeed.com/viewjob?jk=117a26282daa93a0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer: $150-170,000, 5+ Years Required, MN Based, Hybrid - 2 Days in Office</t>
+          <t>Web Data Analyst (Mid–Senior Level)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, MongoDB, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, BigQuery, Git, BigQuery, Power BI, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,217 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c0b8b83d100d40</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Consultant, Cloud Solutions</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Burwood Group</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Camping World</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Lincolnshire, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, AKS, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea3d25d3552f3f14</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Backend Engineer, ML Systems</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Thia</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2bbddda0640b383</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Backend</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Snap Finance</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, EC2, Docker, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05422269350bcaa3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AI Solutions Specialist-Remote Opportunity</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Answer Financial Inc.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Generative AI, LLaMA, Gemini, Copilot, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08437d2060737567</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Software Engineer IV $80,000- $130,000 DOE- Remote</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ELM Utility Services</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acfcda59315648d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2228218d202d65</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-15.xlsx
+++ b/daily_matches/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, Kinesis, MLflow, Apache Airflow, CI/CD, Terraform, Databricks</t>
+          <t>Data Scientist, RAG, Glue, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
+          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Corporate Treasury, Payments Platform, Software Engineering, Associate, NY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, Kinesis, MLflow, Apache Airflow, CI/CD, Terraform, Databricks</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f52b1b3f85fbccca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Corporate Treasury, Payments Platform, Software Engineering, Associate, Dallas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, Kinesis, MLflow, Apache Airflow, CI/CD, Terraform, Databricks</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
+          <t>https://www.indeed.com/viewjob?jk=721e3da7a4ed9569</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, MySQL, MongoDB, Python</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e3a56cc6e6d593</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Scientist, Upstream Development</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ocrolus</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6ab699a2979fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a685d8766c71a32</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Zeitgeist, Personalization</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>sevenhillsgrouptech</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Burlingame, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Dataflow, BigQuery, Python</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Pinecone, Docker, Kubernetes, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f665777ed787bc0c</t>
+          <t>https://www.indeed.com/viewjob?jk=70fb96536754243c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Senior Software Engineer in Test, AI Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Kafka, Hadoop, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03269999a92f7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8e62745232963aca</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Salesforce Platform Architect</t>
+          <t>Senior Python Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Slingshot Aerospace</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R</t>
+          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, Kafka, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b4c7d66e6190b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d381195aacbea3d2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer- Arlington, VA</t>
+          <t>AI/ML Software Engineering - Talent Pipeline</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>FullSteam LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, PyTorch, FastAPI, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896ef6d5605394c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0d162576f7393ef4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Slingshot Aerospace</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ef10fbacb00408</t>
+          <t>https://www.indeed.com/viewjob?jk=4a2dae59fea5b3d5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BioPharma Consulting JAD Group</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Juncos, PR, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Keras, OpenCV, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b2154184df56d96</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist - Production Engineering</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cordial Experience</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Athena, BigQuery, Snowflake, BigQuery, Python, R, Scala</t>
+          <t>S3, EC2, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5485c21d8416d6</t>
+          <t>https://www.indeed.com/viewjob?jk=58d5b920b81f651f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>TensorFlow, PyTorch, S3, Apache Airflow, Snowflake, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6277a4a2f289d56</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Senior Applied ML Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ccbdb3f245768d</t>
+          <t>https://www.indeed.com/viewjob?jk=1678f98f1d271fc6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Quality Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a013f13e8069e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ce4785fb890aa48d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Applied ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=8574541cd497d498</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Agents &amp; Generative AI</t>
+          <t>Senior Applied ML Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vantor</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305217c9c3762b47</t>
+          <t>https://www.indeed.com/viewjob?jk=0d34a3dc359b447f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Agents &amp; Generative AI</t>
+          <t>Senior Applied ML Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vantor</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85021dc7273ef59</t>
+          <t>https://www.indeed.com/viewjob?jk=3000dd6489b0369f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, Git, BigQuery, Python, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29456fe99404592c</t>
+          <t>https://www.indeed.com/viewjob?jk=e77483c11a2ab61a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3677f7a6bce9ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=d957227a721ea1e4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - 1010</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lightcast</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Terraform, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc8d849e742b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d74274da630b92</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - 1010</t>
+          <t>AI Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lightcast</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Terraform, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Keras, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,462 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117a26282daa93a0</t>
+          <t>https://www.indeed.com/viewjob?jk=dd24ea9a69793f26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Web Data Analyst (Mid–Senior Level)</t>
+          <t>Senior Engineer - Asset Protection (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cea5cc14aef02ebc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Glue, Redshift, Data Lake, CI/CD, Git, Redshift, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KeyBank</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brooklyn, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, BigQuery, Power BI, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2228218d202d65</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, BigQuery, Docker, Git, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4101e69cfe9a0df</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>KeyBank</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, BigQuery, Docker, Git, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8ad313dc6f893a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9a31491e18dff73</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ffe1d0742d51504</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Engineer - Digital Experiences &amp; Capabilities</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Git, Hadoop, Tableau, Power BI, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=333e9de0d727160b</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Airtable</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, BigQuery, Snowflake, Databricks, BigQuery, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84c65cead4930ac5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Airtable</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, BigQuery, Snowflake, Databricks, BigQuery, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=018b8d9070ea2321</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LexisNexis Legal &amp; Professional</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58974f6f21aeb331</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Business Intelligence Data Analyst - GPSC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Falls Church, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Jenkins, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=820decca6d67eda0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Thought Machine</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=835d20de2a51358b</t>
         </is>
       </c>
     </row>
